--- a/data/reina/inputs/reina_ff2_SENplus2.xlsx
+++ b/data/reina/inputs/reina_ff2_SENplus2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dfa238\pyproj\gambit_tekken8\data\reina\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B9CD58A-C0A3-4230-9556-B6801C68C38A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56296EED-0116-496B-88DC-7314C0B24F4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13335" yWindow="2700" windowWidth="15900" windowHeight="11925" activeTab="1" xr2:uid="{3646A7B2-A3A2-437C-B2D0-C976E94CCFF6}"/>
+    <workbookView xWindow="-22710" yWindow="945" windowWidth="15900" windowHeight="11925" activeTab="1" xr2:uid="{3646A7B2-A3A2-437C-B2D0-C976E94CCFF6}"/>
   </bookViews>
   <sheets>
     <sheet name="metadata" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t>DB</t>
   </si>
@@ -118,6 +118,15 @@
   </si>
   <si>
     <t>Reina2</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>Hop Kick</t>
+  </si>
+  <si>
+    <t>Crouch Jab</t>
   </si>
 </sst>
 </file>
@@ -546,7 +555,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3B9BB04-D3D2-4E07-A007-5B16E4AB0AD8}">
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.7109375" customWidth="1"/>
@@ -556,9 +565,10 @@
     <col min="7" max="7" width="12.7109375" customWidth="1"/>
     <col min="8" max="8" width="17.42578125" customWidth="1"/>
     <col min="9" max="9" width="12.7109375" customWidth="1"/>
+    <col min="11" max="11" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -586,8 +596,14 @@
       <c r="I1" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J1" t="s">
+        <v>28</v>
+      </c>
+      <c r="K1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -616,7 +632,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -645,7 +661,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -674,7 +690,7 @@
         <v>-74</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -703,7 +719,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -732,7 +748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -761,7 +777,7 @@
         <v>-74</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -790,7 +806,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -817,6 +833,11 @@
       </c>
       <c r="I9">
         <v>-77</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
